--- a/output/cashflow_intelligence.xlsx
+++ b/output/cashflow_intelligence.xlsx
@@ -2888,7 +2888,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>deleveraging</t>
+          <t>financial_institution</t>
         </is>
       </c>
     </row>
